--- a/results/Int Task Remove ACC 0.1/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_6_permute.xlsx
@@ -440,767 +440,767 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5721181576303352</v>
+        <v>0.5479814776913631</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5520410821270421</v>
+        <v>0.5465011349681836</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5551692218955829</v>
+        <v>0.5536865534179287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5682515908160608</v>
+        <v>0.5536865534179287</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5707343337178581</v>
+        <v>0.5382644754958508</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.572046059241618</v>
+        <v>0.5382644754958508</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5499630205038515</v>
+        <v>0.5479547315149035</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5417996222974732</v>
+        <v>0.5431567000334909</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5430648327317382</v>
+        <v>0.5470709448144978</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5101368008782049</v>
+        <v>0.5376888512633498</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5225540040189037</v>
+        <v>0.5408402485766383</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5041491459829568</v>
+        <v>0.5357794068395788</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4814230361329215</v>
+        <v>0.5239855058981133</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.476671519741004</v>
+        <v>0.5174210638931269</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.469938460536598</v>
+        <v>0.521239952740669</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4703443046924423</v>
+        <v>0.5276613608454582</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4835231924236222</v>
+        <v>0.5419368418114836</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4835231924236222</v>
+        <v>0.5223342202210397</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4853140233691809</v>
+        <v>0.5297347709596993</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4846930469244223</v>
+        <v>0.5293289268038552</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4812311613887545</v>
+        <v>0.5468558125255832</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4663777304357534</v>
+        <v>0.5468081345588509</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4869583317828303</v>
+        <v>0.5242959941204927</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4900376307074015</v>
+        <v>0.5248681297212816</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4909679324973021</v>
+        <v>0.5248448721765341</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.457013080043166</v>
+        <v>0.4951903397462136</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4620960164477357</v>
+        <v>0.4825556785621256</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4702140624418562</v>
+        <v>0.4892398969225616</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4758749488334015</v>
+        <v>0.4892398969225616</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4709094630298069</v>
+        <v>0.5095576880139918</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4606191623562684</v>
+        <v>0.5154069605179921</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4609296505786478</v>
+        <v>0.4749830219923343</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4042068246939307</v>
+        <v>0.4782786160830573</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.413923826889443</v>
+        <v>0.4782786160830573</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4327589495032189</v>
+        <v>0.4765598835262159</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4359440702563911</v>
+        <v>0.4765598835262159</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4353696089011275</v>
+        <v>0.4780413891266326</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4276818274848361</v>
+        <v>0.4815986305957652</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4536977170394075</v>
+        <v>0.4872362594425632</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4533418766047705</v>
+        <v>0.4838220518736278</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4521720221039705</v>
+        <v>0.4874525546087151</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4373406858184795</v>
+        <v>0.5113706136270606</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4355952070851784</v>
+        <v>0.4803287686525509</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4452901146131805</v>
+        <v>0.491165621627656</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4471321121571838</v>
+        <v>0.472373525471663</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4500230249693</v>
+        <v>0.4371918375320955</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4640601161016634</v>
+        <v>0.4487706061846463</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4697931008819261</v>
+        <v>0.4487706061846463</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4514591783574591</v>
+        <v>0.4513580080378075</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4514591783574591</v>
+        <v>0.4389919714955532</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4531058125255834</v>
+        <v>0.4634903062553492</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4613645666654262</v>
+        <v>0.4937367431994939</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.45582810813828</v>
+        <v>0.482968499981394</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4659009507684293</v>
+        <v>0.4708408532728017</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4626518717672013</v>
+        <v>0.475065586276188</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.459952833699252</v>
+        <v>0.4634193707438693</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4664009879805009</v>
+        <v>0.4715571856510252</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4830661816693335</v>
+        <v>0.4748516168645109</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4975021396941168</v>
+        <v>0.4547257005172478</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4971451363822424</v>
+        <v>0.4558955550180478</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4986964146169017</v>
+        <v>0.4645334071372753</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4950193967923194</v>
+        <v>0.4713385647303985</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5060271927213188</v>
+        <v>0.4642252446693708</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5101100547017452</v>
+        <v>0.4633437837234399</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5334769099095746</v>
+        <v>0.4544907993152978</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5338350760986864</v>
+        <v>0.4635054236594351</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5289928552822536</v>
+        <v>0.4660474733003386</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5402402039221523</v>
+        <v>0.4615831875860529</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.57659174636252</v>
+        <v>0.4212941428199308</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.57659174636252</v>
+        <v>0.4589888084694675</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.57659174636252</v>
+        <v>0.4617576191716593</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5812711643657202</v>
+        <v>0.476488948014736</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5742252911844603</v>
+        <v>0.4663172608194098</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5350851691288654</v>
+        <v>0.4545012652104342</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5278299780448777</v>
+        <v>0.4824835801734082</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5271834183008968</v>
+        <v>0.4832685223086369</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5271834183008968</v>
+        <v>0.489677138763815</v>
       </c>
     </row>
     <row r="79">
@@ -1210,117 +1210,117 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5271834183008968</v>
+        <v>0.489677138763815</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5241517973430581</v>
+        <v>0.4837104156588398</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5183548543147397</v>
+        <v>0.4829940832806162</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5075145127079225</v>
+        <v>0.4794356789342462</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5099751609422096</v>
+        <v>0.4794356789342462</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4877688572172812</v>
+        <v>0.4811485971049008</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4877688572172812</v>
+        <v>0.4864955066423547</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4953252335057493</v>
+        <v>0.4943507423808283</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4953252335057493</v>
+        <v>0.4512649778588174</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5030397610985003</v>
+        <v>0.5032153555613441</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5111043147397016</v>
+        <v>0.5001348937595356</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.507902913705206</v>
+        <v>0.4997767275704239</v>
       </c>
     </row>
   </sheetData>
